--- a/events/Moscow_2009_JWCH/Moscow_2009_JWCH_Results.xlsx
+++ b/events/Moscow_2009_JWCH/Moscow_2009_JWCH_Results.xlsx
@@ -11933,11 +11933,6 @@
           <t>3:37.918</t>
         </is>
       </c>
-      <c r="R185" t="inlineStr">
-        <is>
-          <t>90936</t>
-        </is>
-      </c>
       <c r="S185" t="inlineStr">
         <is>
           <t>63247</t>
@@ -25495,11 +25490,6 @@
           <t>1:43.486</t>
         </is>
       </c>
-      <c r="R402" t="inlineStr">
-        <is>
-          <t>90936</t>
-        </is>
-      </c>
       <c r="S402" t="inlineStr">
         <is>
           <t>63247</t>
@@ -37296,11 +37286,6 @@
           <t>3:36.906</t>
         </is>
       </c>
-      <c r="R590" t="inlineStr">
-        <is>
-          <t>90936</t>
-        </is>
-      </c>
       <c r="S590" t="inlineStr">
         <is>
           <t>63247</t>
@@ -55911,11 +55896,6 @@
       <c r="P882" t="inlineStr">
         <is>
           <t>1:45.692</t>
-        </is>
-      </c>
-      <c r="R882" t="inlineStr">
-        <is>
-          <t>90936</t>
         </is>
       </c>
       <c r="S882" t="inlineStr">
@@ -69007,7 +68987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D123"/>
+  <dimension ref="A1:D122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70707,17 +70687,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>90936</t>
+          <t>74327</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Sergei</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ALVAREZ LLANO</t>
+          <t>NELOVKO</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -70729,17 +70709,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>74327</t>
+          <t>47191</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sergei</t>
+          <t>Jamesboy Singh</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NELOVKO</t>
+          <t>OINAM</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -70751,17 +70731,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>47191</t>
+          <t>52581</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Jamesboy Singh</t>
+          <t>Brandon Wei Cheng</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>OINAM</t>
+          <t>OOI</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -70773,17 +70753,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>52581</t>
+          <t>175150</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Brandon Wei Cheng</t>
+          <t>Ding Sheng</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>OOI</t>
+          <t>LIM</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -70795,39 +70775,39 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>175150</t>
+          <t>60035</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ding Sheng</t>
+          <t>Carla</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>PEREZ COYA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>60035</t>
+          <t>56159</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Carla</t>
+          <t>Brittany</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PEREZ COYA</t>
+          <t>PETERSEN</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -70839,17 +70819,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>56159</t>
+          <t>50157</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Brittany</t>
+          <t>Gaia</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PETERSEN</t>
+          <t>PIAZZA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -70861,61 +70841,61 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>50157</t>
+          <t>49620</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Gaia</t>
+          <t>Orion</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PIAZZA</t>
+          <t>PILO</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>49620</t>
+          <t>36033</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Orion</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PILO</t>
+          <t>PIPITSOULI</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>36033</t>
+          <t>49622</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Annemia</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PIPITSOULI</t>
+          <t>PRETZMANN</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -70927,39 +70907,39 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>49622</t>
+          <t>49444</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Annemia</t>
+          <t>Javier</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PRETZMANN</t>
+          <t>BERNAL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>49444</t>
+          <t>65040</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Javier</t>
+          <t>Reinier</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BERNAL</t>
+          <t>MORA JIMENEZ</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -70971,17 +70951,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>65040</t>
+          <t>61561</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Reinier</t>
+          <t>Pietro</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MORA JIMENEZ</t>
+          <t>REPELE</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -70993,17 +70973,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>61561</t>
+          <t>36566</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Pietro</t>
+          <t>Manfredi</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>REPELE</t>
+          <t>RIZZA</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -71015,17 +70995,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>36566</t>
+          <t>54783</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Manfredi</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>RIZZA</t>
+          <t>RODEGHER</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -71037,17 +71017,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>54783</t>
+          <t>35862</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Rafal</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>RODEGHER</t>
+          <t>ROSOLSKI</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -71059,17 +71039,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>35862</t>
+          <t>46808</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Rafal</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ROSOLSKI</t>
+          <t>ROSS</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -71081,61 +71061,61 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>46808</t>
+          <t>42483</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ROSS</t>
+          <t>RUSSELL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>42483</t>
+          <t>87442</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Glenn</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>RUSSELL</t>
+          <t>RYPP</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>87442</t>
+          <t>36563</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Glenn</t>
+          <t>Daniele</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>RYPP</t>
+          <t>SANTINI</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -71147,61 +71127,61 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>36563</t>
+          <t>48740</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Daniele</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SANTINI</t>
+          <t>SEGAL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>48740</t>
+          <t>35567</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Mario</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SEGAL</t>
+          <t>SIEGL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>35567</t>
+          <t>54350</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Mario</t>
+          <t>Cosmin</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SIEGL</t>
+          <t>SIMION</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -71213,17 +71193,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>54350</t>
+          <t>35980</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cosmin</t>
+          <t>Jo Sondre</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SIMION</t>
+          <t>SOLHAUG</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -71235,17 +71215,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>35980</t>
+          <t>35917</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Jo Sondre</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SOLHAUG</t>
+          <t>SPALENSKY</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -71257,61 +71237,61 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>35917</t>
+          <t>42146</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Kira</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SPALENSKY</t>
+          <t>STEPANOVA</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>42146</t>
+          <t>35728</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Kira</t>
+          <t>Kostja</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>STEPANOVA</t>
+          <t>STROINSKI</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>35728</t>
+          <t>35934</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Kostja</t>
+          <t>Pawel</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>STROINSKI</t>
+          <t>SZANDRACH</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -71323,17 +71303,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>35934</t>
+          <t>52634</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Pawel</t>
+          <t>Mikhail</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SZANDRACH</t>
+          <t>TAMONOV</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -71345,17 +71325,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>52634</t>
+          <t>42496</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Mikhail</t>
+          <t>Marc</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TAMONOV</t>
+          <t>TARLING</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -71367,17 +71347,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>42496</t>
+          <t>61252</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Marc</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>TARLING</t>
+          <t>TENWOLDE</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -71389,17 +71369,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>61252</t>
+          <t>64637</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Daniil</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>TENWOLDE</t>
+          <t>TETEREV</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -71411,17 +71391,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>64637</t>
+          <t>46841</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Daniil</t>
+          <t>Cristian</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TETEREV</t>
+          <t>TORO</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -71433,17 +71413,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>46841</t>
+          <t>46414</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cristian</t>
+          <t>Ihor</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TORO</t>
+          <t>TRUNOV</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -71455,17 +71435,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>46414</t>
+          <t>44442</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ihor</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TRUNOV</t>
+          <t>VAJDA</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -71477,61 +71457,61 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>44442</t>
+          <t>73769</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Melanie</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>VAJDA</t>
+          <t>VAN NIEKERK</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>73769</t>
+          <t>36672</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Melanie</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>VAN NIEKERK</t>
+          <t>VANDREY</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>36672</t>
+          <t>47426</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Henrik</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>VANDREY</t>
+          <t>VASBANYAI</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -71543,61 +71523,61 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>47426</t>
+          <t>36458</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Henrik</t>
+          <t>Joana</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>VASBANYAI</t>
+          <t>VASCONCELOS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>36458</t>
+          <t>63247</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Joana</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>VASCONCELOS</t>
+          <t>VEGA VEGA</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>63247</t>
+          <t>130380</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Konstantin</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>VEGA VEGA</t>
+          <t>VELKOV</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -71609,17 +71589,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>130380</t>
+          <t>61332</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Konstantin</t>
+          <t>Artem</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>VELKOV</t>
+          <t>VORONKOV</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -71631,17 +71611,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>61332</t>
+          <t>42119</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Artem</t>
+          <t>Aleksei</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>VORONKOV</t>
+          <t>VOSTRIKOV</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -71653,17 +71633,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>42119</t>
+          <t>41792</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Aleksei</t>
+          <t>Joeri</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>VOSTRIKOV</t>
+          <t>WECKX</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -71675,42 +71655,20 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>41792</t>
+          <t>46593</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Joeri</t>
+          <t>Cagribey</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>WECKX</t>
+          <t>YILDIRIM</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>46593</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Cagribey</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>YILDIRIM</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
         <is>
           <t>M</t>
         </is>

--- a/events/Moscow_2009_JWCH/Moscow_2009_JWCH_Results.xlsx
+++ b/events/Moscow_2009_JWCH/Moscow_2009_JWCH_Results.xlsx
@@ -1527,6 +1527,11 @@
           <t>4:27.526</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3438,6 +3443,11 @@
           <t>3:49.605</t>
         </is>
       </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>46268</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3800,6 +3810,11 @@
           <t>3:40.081</t>
         </is>
       </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>45211</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4610,6 +4625,11 @@
           <t>3:50.033</t>
         </is>
       </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>103245</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6647,6 +6667,11 @@
           <t>35917</t>
         </is>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6842,6 +6867,11 @@
           <t>3:56.285</t>
         </is>
       </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>94190</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7087,6 +7117,11 @@
           <t>3:37.467</t>
         </is>
       </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8089,6 +8124,11 @@
           <t>3:21.974</t>
         </is>
       </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>46843</t>
+        </is>
+      </c>
       <c r="S123" t="inlineStr">
         <is>
           <t>46823</t>
@@ -9211,6 +9251,11 @@
           <t>3:19.251</t>
         </is>
       </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>127254</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -11498,6 +11543,11 @@
           <t>3:34.193</t>
         </is>
       </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>63214</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -11623,6 +11673,11 @@
           <t>42496</t>
         </is>
       </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>42487</t>
+        </is>
+      </c>
       <c r="U180" t="inlineStr">
         <is>
           <t>75889</t>
@@ -12008,6 +12063,11 @@
           <t>3:39.381</t>
         </is>
       </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>52609</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -12705,6 +12765,11 @@
           <t>3:14.983</t>
         </is>
       </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>53065</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -14564,6 +14629,11 @@
           <t>1:52.494</t>
         </is>
       </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -15179,6 +15249,11 @@
           <t>1:44.468</t>
         </is>
       </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>44432</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -15364,6 +15439,11 @@
           <t>1:45.948</t>
         </is>
       </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>46268</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -15489,6 +15569,11 @@
           <t>1:48.072</t>
         </is>
       </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>103245</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -19862,6 +19947,11 @@
           <t>1:43.310</t>
         </is>
       </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -19927,6 +20017,11 @@
           <t>35917</t>
         </is>
       </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -20117,6 +20212,11 @@
           <t>46808</t>
         </is>
       </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -20999,6 +21099,11 @@
           <t>75889</t>
         </is>
       </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>42487</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -22301,6 +22406,11 @@
           <t>1:32.705</t>
         </is>
       </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>46843</t>
+        </is>
+      </c>
       <c r="S351" t="inlineStr">
         <is>
           <t>46823</t>
@@ -22676,6 +22786,11 @@
           <t>1:31.974</t>
         </is>
       </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>45211</t>
+        </is>
+      </c>
       <c r="S357" t="inlineStr">
         <is>
           <t>47424</t>
@@ -24940,6 +25055,11 @@
           <t>42496</t>
         </is>
       </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>42487</t>
+        </is>
+      </c>
       <c r="U393" t="inlineStr">
         <is>
           <t>75889</t>
@@ -25005,6 +25125,11 @@
           <t>1:45.142</t>
         </is>
       </c>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>63214</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -25430,6 +25555,11 @@
           <t>1:42.893</t>
         </is>
       </c>
+      <c r="T401" t="inlineStr">
+        <is>
+          <t>52609</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -26272,6 +26402,11 @@
           <t>1:24.413</t>
         </is>
       </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>127254</t>
+        </is>
+      </c>
       <c r="U414" t="inlineStr">
         <is>
           <t>45210</t>
@@ -26777,6 +26912,11 @@
           <t>1:34.062</t>
         </is>
       </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>53065</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -27887,6 +28027,11 @@
           <t>1:39.378</t>
         </is>
       </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>73250</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -28392,6 +28537,11 @@
           <t>1:41.324</t>
         </is>
       </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -29132,6 +29282,11 @@
           <t>4:36.198</t>
         </is>
       </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -30547,6 +30702,11 @@
           <t>3:54.238</t>
         </is>
       </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>103245</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -30789,6 +30949,11 @@
       <c r="N486" t="n">
         <v>9</v>
       </c>
+      <c r="R486" t="inlineStr">
+        <is>
+          <t>46268</t>
+        </is>
+      </c>
       <c r="X486" t="inlineStr">
         <is>
           <t>DSQ</t>
@@ -31484,6 +31649,11 @@
           <t>3:40.352</t>
         </is>
       </c>
+      <c r="R497" t="inlineStr">
+        <is>
+          <t>45211</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -33714,6 +33884,11 @@
           <t>3:52.058</t>
         </is>
       </c>
+      <c r="R533" t="inlineStr">
+        <is>
+          <t>94190</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -34776,6 +34951,11 @@
           <t>3:23.494</t>
         </is>
       </c>
+      <c r="R550" t="inlineStr">
+        <is>
+          <t>46843</t>
+        </is>
+      </c>
       <c r="S550" t="inlineStr">
         <is>
           <t>46823</t>
@@ -35346,6 +35526,11 @@
           <t>3:21.593</t>
         </is>
       </c>
+      <c r="S559" t="inlineStr">
+        <is>
+          <t>127254</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -37161,6 +37346,11 @@
           <t>3:36.888</t>
         </is>
       </c>
+      <c r="T588" t="inlineStr">
+        <is>
+          <t>63214</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -37366,6 +37556,11 @@
           <t>42496</t>
         </is>
       </c>
+      <c r="S591" t="inlineStr">
+        <is>
+          <t>42487</t>
+        </is>
+      </c>
       <c r="U591" t="inlineStr">
         <is>
           <t>75889</t>
@@ -37551,6 +37746,11 @@
           <t>4:19.806</t>
         </is>
       </c>
+      <c r="U594" t="inlineStr">
+        <is>
+          <t>52609</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -39113,6 +39313,11 @@
           <t>3:47.577</t>
         </is>
       </c>
+      <c r="R618" t="inlineStr">
+        <is>
+          <t>103245</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -43494,6 +43699,11 @@
           <t>3:35.771</t>
         </is>
       </c>
+      <c r="R686" t="inlineStr">
+        <is>
+          <t>45211</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -44593,6 +44803,11 @@
           <t>3:37.625</t>
         </is>
       </c>
+      <c r="R703" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -44732,6 +44947,11 @@
           <t>35917</t>
         </is>
       </c>
+      <c r="S705" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -45129,6 +45349,11 @@
           <t>3:50.780</t>
         </is>
       </c>
+      <c r="R711" t="inlineStr">
+        <is>
+          <t>94190</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -45191,6 +45416,11 @@
           <t>3:19.405</t>
         </is>
       </c>
+      <c r="S712" t="inlineStr">
+        <is>
+          <t>127254</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -45377,6 +45607,11 @@
           <t>3:22.714</t>
         </is>
       </c>
+      <c r="R715" t="inlineStr">
+        <is>
+          <t>46843</t>
+        </is>
+      </c>
       <c r="S715" t="inlineStr">
         <is>
           <t>46823</t>
@@ -46850,6 +47085,11 @@
       <c r="N738" t="n">
         <v>9</v>
       </c>
+      <c r="T738" t="inlineStr">
+        <is>
+          <t>63214</t>
+        </is>
+      </c>
       <c r="X738" t="inlineStr">
         <is>
           <t>DSQ</t>
@@ -48168,6 +48408,11 @@
           <t>1:57.230</t>
         </is>
       </c>
+      <c r="R758" t="inlineStr">
+        <is>
+          <t>94190</t>
+        </is>
+      </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
@@ -48853,6 +49098,11 @@
           <t>1:46.568</t>
         </is>
       </c>
+      <c r="R769" t="inlineStr">
+        <is>
+          <t>44432</t>
+        </is>
+      </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
@@ -48913,6 +49163,11 @@
           <t>1:48.378</t>
         </is>
       </c>
+      <c r="R770" t="inlineStr">
+        <is>
+          <t>46268</t>
+        </is>
+      </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
@@ -50158,6 +50413,11 @@
           <t>1:49.395</t>
         </is>
       </c>
+      <c r="R790" t="inlineStr">
+        <is>
+          <t>103245</t>
+        </is>
+      </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -52398,6 +52658,11 @@
           <t>46808</t>
         </is>
       </c>
+      <c r="S826" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
@@ -52643,6 +52908,11 @@
           <t>35917</t>
         </is>
       </c>
+      <c r="S830" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
@@ -52838,6 +53108,11 @@
           <t>75889</t>
         </is>
       </c>
+      <c r="S833" t="inlineStr">
+        <is>
+          <t>42487</t>
+        </is>
+      </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
@@ -53023,6 +53298,11 @@
           <t>1:34.634</t>
         </is>
       </c>
+      <c r="R836" t="inlineStr">
+        <is>
+          <t>45211</t>
+        </is>
+      </c>
       <c r="S836" t="inlineStr">
         <is>
           <t>47424</t>
@@ -54148,6 +54428,11 @@
           <t>1:35.860</t>
         </is>
       </c>
+      <c r="R854" t="inlineStr">
+        <is>
+          <t>46843</t>
+        </is>
+      </c>
       <c r="S854" t="inlineStr">
         <is>
           <t>46823</t>
@@ -56043,6 +56328,11 @@
           <t>1:47.010</t>
         </is>
       </c>
+      <c r="T884" t="inlineStr">
+        <is>
+          <t>52609</t>
+        </is>
+      </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
@@ -56108,6 +56398,11 @@
           <t>42496</t>
         </is>
       </c>
+      <c r="S885" t="inlineStr">
+        <is>
+          <t>42487</t>
+        </is>
+      </c>
       <c r="U885" t="inlineStr">
         <is>
           <t>75889</t>
@@ -58122,6 +58417,11 @@
           <t>1:44.007</t>
         </is>
       </c>
+      <c r="U916" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
@@ -58824,6 +59124,11 @@
           <t>1:48.887</t>
         </is>
       </c>
+      <c r="R927" t="inlineStr">
+        <is>
+          <t>46268</t>
+        </is>
+      </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
@@ -59007,6 +59312,11 @@
       <c r="N930" t="n">
         <v>9</v>
       </c>
+      <c r="R930" t="inlineStr">
+        <is>
+          <t>103245</t>
+        </is>
+      </c>
       <c r="X930" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -59838,6 +60148,11 @@
           <t>1:45.561</t>
         </is>
       </c>
+      <c r="R943" t="inlineStr">
+        <is>
+          <t>44432</t>
+        </is>
+      </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
@@ -60798,6 +61113,11 @@
           <t>75889</t>
         </is>
       </c>
+      <c r="S958" t="inlineStr">
+        <is>
+          <t>42487</t>
+        </is>
+      </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
@@ -61247,6 +61567,11 @@
           <t>46808</t>
         </is>
       </c>
+      <c r="S965" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
@@ -63703,6 +64028,11 @@
           <t>1:51.286</t>
         </is>
       </c>
+      <c r="R1003" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
     </row>
     <row r="1004">
       <c r="A1004" t="inlineStr">
@@ -63961,6 +64291,11 @@
           <t>1:55.826</t>
         </is>
       </c>
+      <c r="R1007" t="inlineStr">
+        <is>
+          <t>94190</t>
+        </is>
+      </c>
     </row>
     <row r="1008">
       <c r="A1008" t="inlineStr">
@@ -65447,6 +65782,11 @@
           <t>1:42.050</t>
         </is>
       </c>
+      <c r="R1030" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
     </row>
     <row r="1031">
       <c r="A1031" t="inlineStr">
@@ -65849,6 +66189,11 @@
           <t>35917</t>
         </is>
       </c>
+      <c r="S1036" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="1037">
       <c r="A1037" t="inlineStr">
@@ -66097,6 +66442,11 @@
           <t>1:34.077</t>
         </is>
       </c>
+      <c r="R1040" t="inlineStr">
+        <is>
+          <t>45211</t>
+        </is>
+      </c>
       <c r="S1040" t="inlineStr">
         <is>
           <t>47424</t>
@@ -66370,6 +66720,11 @@
           <t>1:35.564</t>
         </is>
       </c>
+      <c r="R1044" t="inlineStr">
+        <is>
+          <t>46843</t>
+        </is>
+      </c>
       <c r="S1044" t="inlineStr">
         <is>
           <t>46823</t>
@@ -67806,6 +68161,11 @@
           <t>1:22.002</t>
         </is>
       </c>
+      <c r="T1066" t="inlineStr">
+        <is>
+          <t>127254</t>
+        </is>
+      </c>
       <c r="U1066" t="inlineStr">
         <is>
           <t>45210</t>
@@ -68506,6 +68866,11 @@
           <t>1:38.364</t>
         </is>
       </c>
+      <c r="T1076" t="inlineStr">
+        <is>
+          <t>73250</t>
+        </is>
+      </c>
     </row>
     <row r="1077">
       <c r="A1077" t="inlineStr">
@@ -68973,6 +69338,11 @@
       <c r="P1083" t="inlineStr">
         <is>
           <t>1:45.061</t>
+        </is>
+      </c>
+      <c r="U1083" t="inlineStr">
+        <is>
+          <t>42058</t>
         </is>
       </c>
     </row>
@@ -68987,7 +69357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D122"/>
+  <dimension ref="A1:D138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71674,6 +72044,358 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>DRAHOKOUPIL</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Alexey</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>KOROVASHKOV</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Volha</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>KHUDZENKA</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>42487</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Jason Stephen Reginald</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>MCCOOMBS</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>44432</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Miroslav</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ZATKO</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>45211</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Tibor</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>HUFNAGEL</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>46268</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>VALENCIA</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>46843</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>GARROTE</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>52609</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Stepan</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>LARIONOV</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>HEFNER</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>53065</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Christopher</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>MILLER</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>63214</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Nurislom</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>TUKHTASIN UGLI</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>73250</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Isabel</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>FRIEDT</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>94190</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Vitalii</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>GOLIUK</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>103245</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Ching Ching Singh</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>ARAMBAM</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>127254</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Gabor</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>SZABO</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Moscow_2009_JWCH/Moscow_2009_JWCH_Results.xlsx
+++ b/events/Moscow_2009_JWCH/Moscow_2009_JWCH_Results.xlsx
@@ -11993,11 +11993,6 @@
           <t>63247</t>
         </is>
       </c>
-      <c r="T185" t="inlineStr">
-        <is>
-          <t>46822</t>
-        </is>
-      </c>
       <c r="U185" t="inlineStr">
         <is>
           <t>49444</t>
@@ -25625,11 +25620,6 @@
           <t>63247</t>
         </is>
       </c>
-      <c r="T402" t="inlineStr">
-        <is>
-          <t>46822</t>
-        </is>
-      </c>
       <c r="U402" t="inlineStr">
         <is>
           <t>49444</t>
@@ -37481,11 +37471,6 @@
           <t>63247</t>
         </is>
       </c>
-      <c r="T590" t="inlineStr">
-        <is>
-          <t>46822</t>
-        </is>
-      </c>
       <c r="U590" t="inlineStr">
         <is>
           <t>49444</t>
@@ -56186,11 +56171,6 @@
       <c r="S882" t="inlineStr">
         <is>
           <t>63247</t>
-        </is>
-      </c>
-      <c r="T882" t="inlineStr">
-        <is>
-          <t>46822</t>
         </is>
       </c>
       <c r="U882" t="inlineStr">
@@ -69357,7 +69337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D138"/>
+  <dimension ref="A1:D137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70837,61 +70817,61 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>46822</t>
+          <t>46674</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Manuel Antonio</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>MACHOVA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>46674</t>
+          <t>58229</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Stuart</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MACHOVA</t>
+          <t>MACLAREN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>58229</t>
+          <t>42660</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Stuart</t>
+          <t>Pierrick</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MACLAREN</t>
+          <t>MARTIN</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -70903,17 +70883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>42660</t>
+          <t>42046</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Pierrick</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MARTIN</t>
+          <t>MIADZVEDZEU</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -70925,17 +70905,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>42046</t>
+          <t>44426</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Matej</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MIADZVEDZEU</t>
+          <t>MICHALEK</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -70947,17 +70927,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>44426</t>
+          <t>35992</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Matej</t>
+          <t>Morten</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MICHALEK</t>
+          <t>MINDE</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -70969,105 +70949,105 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>35992</t>
+          <t>49716</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Morten</t>
+          <t>Lucia</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MINDE</t>
+          <t>MISTINOVA</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>49716</t>
+          <t>63968</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Lucia</t>
+          <t>Yusuke</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MISTINOVA</t>
+          <t>MIYATA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>63968</t>
+          <t>36412</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Yusuke</t>
+          <t>Maricela</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MIYATA</t>
+          <t>MONTEMAYOR RODRIGUEZ</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>36412</t>
+          <t>74327</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Maricela</t>
+          <t>Sergei</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MONTEMAYOR RODRIGUEZ</t>
+          <t>NELOVKO</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>74327</t>
+          <t>47191</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sergei</t>
+          <t>Jamesboy Singh</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NELOVKO</t>
+          <t>OINAM</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -71079,17 +71059,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>47191</t>
+          <t>52581</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Jamesboy Singh</t>
+          <t>Brandon Wei Cheng</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OINAM</t>
+          <t>OOI</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -71101,17 +71081,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>52581</t>
+          <t>175150</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Brandon Wei Cheng</t>
+          <t>Ding Sheng</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>OOI</t>
+          <t>LIM</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -71123,39 +71103,39 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>175150</t>
+          <t>60035</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ding Sheng</t>
+          <t>Carla</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LIM</t>
+          <t>PEREZ COYA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>60035</t>
+          <t>56159</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Carla</t>
+          <t>Brittany</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PEREZ COYA</t>
+          <t>PETERSEN</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -71167,17 +71147,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>56159</t>
+          <t>50157</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Brittany</t>
+          <t>Gaia</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PETERSEN</t>
+          <t>PIAZZA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -71189,61 +71169,61 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>50157</t>
+          <t>49620</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Gaia</t>
+          <t>Orion</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PIAZZA</t>
+          <t>PILO</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>49620</t>
+          <t>36033</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Orion</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PILO</t>
+          <t>PIPITSOULI</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>36033</t>
+          <t>49622</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Annemia</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PIPITSOULI</t>
+          <t>PRETZMANN</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -71255,39 +71235,39 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>49622</t>
+          <t>49444</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Annemia</t>
+          <t>Javier</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PRETZMANN</t>
+          <t>BERNAL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>49444</t>
+          <t>65040</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Javier</t>
+          <t>Reinier</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BERNAL</t>
+          <t>MORA JIMENEZ</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -71299,17 +71279,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>65040</t>
+          <t>61561</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Reinier</t>
+          <t>Pietro</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MORA JIMENEZ</t>
+          <t>REPELE</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -71321,17 +71301,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>61561</t>
+          <t>36566</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Pietro</t>
+          <t>Manfredi</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>REPELE</t>
+          <t>RIZZA</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -71343,17 +71323,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>36566</t>
+          <t>54783</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Manfredi</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>RIZZA</t>
+          <t>RODEGHER</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -71365,17 +71345,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>54783</t>
+          <t>35862</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Rafal</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>RODEGHER</t>
+          <t>ROSOLSKI</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -71387,17 +71367,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>35862</t>
+          <t>46808</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Rafal</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ROSOLSKI</t>
+          <t>ROSS</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -71409,61 +71389,61 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>46808</t>
+          <t>42483</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ROSS</t>
+          <t>RUSSELL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>42483</t>
+          <t>87442</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Glenn</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>RUSSELL</t>
+          <t>RYPP</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>87442</t>
+          <t>36563</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Glenn</t>
+          <t>Daniele</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>RYPP</t>
+          <t>SANTINI</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -71475,61 +71455,61 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>36563</t>
+          <t>48740</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Daniele</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SANTINI</t>
+          <t>SEGAL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>48740</t>
+          <t>35567</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Mario</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SEGAL</t>
+          <t>SIEGL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>35567</t>
+          <t>54350</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Mario</t>
+          <t>Cosmin</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SIEGL</t>
+          <t>SIMION</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -71541,17 +71521,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>54350</t>
+          <t>35980</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cosmin</t>
+          <t>Jo Sondre</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SIMION</t>
+          <t>SOLHAUG</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -71563,17 +71543,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>35980</t>
+          <t>35917</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Jo Sondre</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SOLHAUG</t>
+          <t>SPALENSKY</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -71585,61 +71565,61 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>35917</t>
+          <t>42146</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Kira</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SPALENSKY</t>
+          <t>STEPANOVA</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>42146</t>
+          <t>35728</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Kira</t>
+          <t>Kostja</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>STEPANOVA</t>
+          <t>STROINSKI</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>35728</t>
+          <t>35934</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Kostja</t>
+          <t>Pawel</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>STROINSKI</t>
+          <t>SZANDRACH</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -71651,17 +71631,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>35934</t>
+          <t>52634</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Pawel</t>
+          <t>Mikhail</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SZANDRACH</t>
+          <t>TAMONOV</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -71673,17 +71653,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>52634</t>
+          <t>42496</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Mikhail</t>
+          <t>Marc</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>TAMONOV</t>
+          <t>TARLING</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -71695,17 +71675,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>42496</t>
+          <t>61252</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Marc</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TARLING</t>
+          <t>TENWOLDE</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -71717,17 +71697,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>61252</t>
+          <t>64637</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Daniil</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>TENWOLDE</t>
+          <t>TETEREV</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -71739,17 +71719,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>64637</t>
+          <t>46841</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Daniil</t>
+          <t>Cristian</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>TETEREV</t>
+          <t>TORO</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -71761,17 +71741,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>46841</t>
+          <t>46414</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cristian</t>
+          <t>Ihor</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TORO</t>
+          <t>TRUNOV</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -71783,17 +71763,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>46414</t>
+          <t>44442</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ihor</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TRUNOV</t>
+          <t>VAJDA</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -71805,61 +71785,61 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>44442</t>
+          <t>73769</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Melanie</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>VAJDA</t>
+          <t>VAN NIEKERK</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>73769</t>
+          <t>36672</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Melanie</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>VAN NIEKERK</t>
+          <t>VANDREY</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>36672</t>
+          <t>47426</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Henrik</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>VANDREY</t>
+          <t>VASBANYAI</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -71871,61 +71851,61 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>47426</t>
+          <t>36458</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Henrik</t>
+          <t>Joana</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>VASBANYAI</t>
+          <t>VASCONCELOS</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>36458</t>
+          <t>63247</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Joana</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>VASCONCELOS</t>
+          <t>VEGA VEGA</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>63247</t>
+          <t>130380</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Konstantin</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>VEGA VEGA</t>
+          <t>VELKOV</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -71937,17 +71917,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>130380</t>
+          <t>61332</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Konstantin</t>
+          <t>Artem</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>VELKOV</t>
+          <t>VORONKOV</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -71959,17 +71939,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>61332</t>
+          <t>42119</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Artem</t>
+          <t>Aleksei</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>VORONKOV</t>
+          <t>VOSTRIKOV</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -71981,17 +71961,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>42119</t>
+          <t>41792</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Aleksei</t>
+          <t>Joeri</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>VOSTRIKOV</t>
+          <t>WECKX</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -72003,17 +71983,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>41792</t>
+          <t>46593</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Joeri</t>
+          <t>Cagribey</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>WECKX</t>
+          <t>YILDIRIM</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -72025,17 +72005,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>46593</t>
+          <t>35898</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Cagribey</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>YILDIRIM</t>
+          <t>DRAHOKOUPIL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -72047,17 +72027,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>35898</t>
+          <t>36161</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Alexey</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>DRAHOKOUPIL</t>
+          <t>KOROVASHKOV</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -72069,61 +72049,61 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>36161</t>
+          <t>42058</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Alexey</t>
+          <t>Volha</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>KOROVASHKOV</t>
+          <t>KHUDZENKA</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>42058</t>
+          <t>42487</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Volha</t>
+          <t>Jason Stephen Reginald</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>KHUDZENKA</t>
+          <t>MCCOOMBS</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>42487</t>
+          <t>44432</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Jason Stephen Reginald</t>
+          <t>Miroslav</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MCCOOMBS</t>
+          <t>ZATKO</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -72135,17 +72115,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>44432</t>
+          <t>45211</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Miroslav</t>
+          <t>Tibor</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ZATKO</t>
+          <t>HUFNAGEL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -72157,17 +72137,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>45211</t>
+          <t>46268</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Tibor</t>
+          <t>Miguel</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>HUFNAGEL</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -72179,17 +72159,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>46268</t>
+          <t>46843</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Miguel</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>GARROTE</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -72201,17 +72181,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>46843</t>
+          <t>52609</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Stepan</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>GARROTE</t>
+          <t>LARIONOV</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -72223,17 +72203,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>52609</t>
+          <t>53064</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Stepan</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>LARIONOV</t>
+          <t>HEFNER</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -72245,17 +72225,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>53064</t>
+          <t>53065</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Christopher</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>HEFNER</t>
+          <t>MILLER</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -72267,17 +72247,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>53065</t>
+          <t>63214</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Christopher</t>
+          <t>Nurislom</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MILLER</t>
+          <t>TUKHTASIN UGLI</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -72289,61 +72269,61 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>63214</t>
+          <t>73250</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Nurislom</t>
+          <t>Isabel</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>TUKHTASIN UGLI</t>
+          <t>FRIEDT</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>73250</t>
+          <t>94190</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Isabel</t>
+          <t>Vitalii</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FRIEDT</t>
+          <t>GOLIUK</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>94190</t>
+          <t>103245</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Vitalii</t>
+          <t>Ching Ching Singh</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>GOLIUK</t>
+          <t>ARAMBAM</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -72355,42 +72335,20 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>103245</t>
+          <t>127254</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ching Ching Singh</t>
+          <t>Gabor</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ARAMBAM</t>
+          <t>SZABO</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>127254</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Gabor</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>SZABO</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
         <is>
           <t>M</t>
         </is>

--- a/events/Moscow_2009_JWCH/Moscow_2009_JWCH_Results.xlsx
+++ b/events/Moscow_2009_JWCH/Moscow_2009_JWCH_Results.xlsx
@@ -5425,6 +5425,11 @@
           <t>4:11.616</t>
         </is>
       </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>36671</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -11288,6 +11293,11 @@
           <t>3:25.501</t>
         </is>
       </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>36183</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -11803,6 +11813,11 @@
           <t>3:28.682</t>
         </is>
       </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>68347</t>
+        </is>
+      </c>
       <c r="U182" t="inlineStr">
         <is>
           <t>54350</t>
@@ -23775,6 +23790,11 @@
           <t>42519</t>
         </is>
       </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>36671</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -25365,6 +25385,11 @@
           <t>1:38.249</t>
         </is>
       </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>68347</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -33324,6 +33349,11 @@
           <t>4:11.038</t>
         </is>
       </c>
+      <c r="R524" t="inlineStr">
+        <is>
+          <t>36671</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -46562,6 +46592,11 @@
           <t>3:36.738</t>
         </is>
       </c>
+      <c r="S730" t="inlineStr">
+        <is>
+          <t>68347</t>
+        </is>
+      </c>
       <c r="U730" t="inlineStr">
         <is>
           <t>54350</t>
@@ -46691,6 +46726,11 @@
           <t>3:38.518</t>
         </is>
       </c>
+      <c r="R732" t="inlineStr">
+        <is>
+          <t>36183</t>
+        </is>
+      </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -67817,6 +67857,11 @@
       <c r="P1061" t="inlineStr">
         <is>
           <t>1:38.037</t>
+        </is>
+      </c>
+      <c r="R1061" t="inlineStr">
+        <is>
+          <t>68347</t>
         </is>
       </c>
     </row>
@@ -69337,7 +69382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72354,6 +72399,50 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>36183</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Rasul</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>ISHMUCHAMEDOV</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>68347</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Andrei</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>LIFERY</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
